--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:34</t>
+          <t>2026-09-03 00:52:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:35</t>
+          <t>2026-09-03 00:52:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:37</t>
+          <t>2026-09-03 00:52:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:38</t>
+          <t>2026-09-03 00:52:53</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:49</t>
+          <t>2026-09-03 01:13:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:50</t>
+          <t>2026-09-03 01:13:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:52</t>
+          <t>2026-09-03 01:13:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:53</t>
+          <t>2026-09-03 01:13:08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.59%10,500,000</t>
+          <t>15.99%10,500,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.59%</t>
+          <t>15.99%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.49%3,150,000</t>
+          <t>6.62%3,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.49%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.62%2,110,000</t>
+          <t>5.84%2,110,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.43%1,600,000</t>
+          <t>5.39%1,600,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.13%8,460,000</t>
+          <t>4.98%8,460,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>4.98%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.01%1,115,000</t>
+          <t>3.99%1,115,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7810</v>
+        <v>125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.94%810,000</t>
+          <t>3.98%50,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>810000</v>
+        <v>50000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>126</v>
+        <v>7150</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.92%50,000,000</t>
+          <t>3.69%810,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50000000</v>
+        <v>810000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.62%1,100,000</t>
+          <t>3.54%1,100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.39%2,087,956</t>
+          <t>3.29%2,087,956</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2140</v>
+        <v>1760</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.07%2,307,000</t>
+          <t>3.08%2,750,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2307000</v>
+        <v>2750000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1730</v>
+        <v>2090</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.96%2,750,000</t>
+          <t>3.07%2,307,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2750000</v>
+        <v>2307000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.69%8,000,000</t>
+          <t>2.61%8,000,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.39%650,000</t>
+          <t>2.40%650,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:04</t>
+          <t>2026-09-03 21:25:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>17725</v>
+        <v>17850</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.09%189,500</t>
+          <t>2.39%210,500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>189500</v>
+        <v>210500</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.28%237.5</t>
+          <t>-6.95%221</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237.5</v>
+        <v>221</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.00%13,500,000</t>
+          <t>1.90%13,500,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%2,640,000</t>
+          <t>1.82%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,34 +1541,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.09%847</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>847</v>
+        <v>2100</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.79%3,400,000</t>
+          <t>1.73%1,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3400000</v>
+        <v>1293000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2170</v>
+        <v>589</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.75%1,293,000</t>
+          <t>1.69%4,500,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1293000</v>
+        <v>4500000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-8.5%775</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>967</v>
+        <v>775</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.69%2,800,000</t>
+          <t>1.68%3,400,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2800000</v>
+        <v>3400000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>-4.14%927</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1410</v>
+        <v>927</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.67%1,900,000</t>
+          <t>1.65%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1900000</v>
+        <v>2800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>589</v>
+        <v>1345</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.65%4,500,000</t>
+          <t>1.63%1,900,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4500000</v>
+        <v>1900000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.37%1,737,000</t>
+          <t>1.31%1,737,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.23%1,000,000</t>
+          <t>1.28%1,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>-1.08%275</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2110</v>
+        <v>275</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.12%850,000</t>
+          <t>0.94%5,360,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>850000</v>
+        <v>5360000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.11%278</t>
+          <t>-0.71%2095</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>278</v>
+        <v>2095</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.93%5,360,000</t>
+          <t>0.87%650,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5360000</v>
+        <v>650000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.7%179</t>
+          <t>-5.59%169</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.56%5,000,000</t>
+          <t>0.54%5,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-1.39%247.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.45%392</t>
+          <t>+2.8%5870</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>392</v>
+        <v>5870</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.49%2,000,000</t>
+          <t>0.49%130,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2000000</v>
+        <v>130000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:05</t>
+          <t>2026-09-03 21:25:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.73%5710</t>
+          <t>-4.34%375</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>-4.34%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5710</v>
+        <v>375</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.46%130,000</t>
+          <t>0.48%2,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>130000</v>
+        <v>2000000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.68%602</t>
+          <t>-1.39%1770</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>602</v>
+        <v>1770</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.41%1,100,000</t>
+          <t>0.39%350,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1100000</v>
+        <v>350000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.07%757</t>
+          <t>-7.97%554</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-7.97%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>757</v>
+        <v>554</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.38%800,000</t>
+          <t>0.39%1,100,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>800000</v>
+        <v>1100000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-1.98%742</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-1.98%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>13865</v>
+        <v>742</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.30%35,000</t>
+          <t>0.38%800,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>35000</v>
+        <v>800000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>270.5</v>
+        <v>13450</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.29%1,700,000</t>
+          <t>0.30%35,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1700000</v>
+        <v>35000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.29%1705</t>
+          <t>+3.21%112.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1705</v>
+        <v>112.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.27%250,000</t>
+          <t>0.29%4,000,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>250000</v>
+        <v>4000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.79%1795</t>
+          <t>-3.51%261</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.79%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1795</v>
+        <v>261</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.25%225,000</t>
+          <t>0.28%1,700,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>225000</v>
+        <v>1700000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.6%80.8</t>
+          <t>-2.05%1670</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>80.8</v>
+        <v>1670</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.16%3,100,000</t>
+          <t>0.27%250,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3100000</v>
+        <v>250000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-6.82%1025</t>
+          <t>+0.98%1035</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.82%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.41%123</t>
+          <t>-4.95%76.8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-4.95%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>123</v>
+        <v>76.8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.15%2,000,000</t>
+          <t>0.15%3,100,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2000000</v>
+        <v>3100000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.37%503</t>
+          <t>-4.88%117</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>503</v>
+        <v>117</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.13%400,000</t>
+          <t>0.15%2,000,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>400000</v>
+        <v>2000000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.38%704</t>
+          <t>+0.99%711</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.13%300,000</t>
+          <t>0.14%300,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.44%542</t>
+          <t>-3.14%525</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.68%233.5</t>
+          <t>+5.41%156</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>+5.41%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>233.5</v>
+        <v>156</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.10%700,000</t>
+          <t>0.13%1,351,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>700000</v>
+        <v>1351000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.8%109</t>
+          <t>-6.56%470</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-6.56%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>109</v>
+        <v>470</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.08%1,200,000</t>
+          <t>0.12%400,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:06</t>
+          <t>2026-09-03 21:25:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.17%579</t>
+          <t>-3.21%226</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>579</v>
+        <v>226</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08%220,000</t>
+          <t>0.10%700,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>220000</v>
+        <v>700000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.83%315</t>
+          <t>-5.08%299</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.41%245.5</t>
+          <t>-4.89%233.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-4.89%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>245.5</v>
+        <v>233.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>-3.63%558</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2065</v>
+        <v>558</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.01%16,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.96%492</t>
+          <t>-3.15%2000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>492</v>
+        <v>2000</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>+1.63%500</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:08</t>
+          <t>2026-09-03 21:25:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.95%352</t>
+          <t>-2.13%344.5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>352</v>
+        <v>344.5</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3589,67 +3589,6 @@
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-03 01:13:08</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2481強茂</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-5.73%148</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-5.73%</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>148</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:26</t>
+          <t>2026-09-03 21:40:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:28</t>
+          <t>2026-09-03 21:40:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:29</t>
+          <t>2026-09-03 21:40:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:30</t>
+          <t>2026-09-03 21:40:12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:08</t>
+          <t>2026-09-03 21:56:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:10</t>
+          <t>2026-09-03 21:56:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:11</t>
+          <t>2026-09-03 21:56:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:12</t>
+          <t>2026-09-03 21:56:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:02</t>
+          <t>2026-09-03 22:44:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:03</t>
+          <t>2026-09-03 22:44:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:04</t>
+          <t>2026-09-03 22:44:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:56:06</t>
+          <t>2026-09-03 22:44:44</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:40</t>
+          <t>2026-09-03 23:00:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:41</t>
+          <t>2026-09-03 23:00:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:43</t>
+          <t>2026-09-03 23:00:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:44</t>
+          <t>2026-09-03 23:00:34</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
